--- a/analysis/data/PRISM_vs_nmr.xlsx
+++ b/analysis/data/PRISM_vs_nmr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,10 +454,20 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>n_replicates</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n_usable</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>rate_class</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>class_source</t>
         </is>
@@ -485,12 +495,14 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -518,12 +530,14 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -550,19 +564,25 @@
         <v>82.6823</v>
       </c>
       <c r="F4" t="n">
-        <v>98.4615384615384</v>
+        <v>144.9314603705081</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -589,19 +609,25 @@
         <v>6.1377</v>
       </c>
       <c r="F5" t="n">
-        <v>6.36815920398009</v>
+        <v>6.368159203980089</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -629,12 +655,14 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -661,19 +689,25 @@
         <v>18.6814</v>
       </c>
       <c r="F7" t="n">
-        <v>23.6004380326619</v>
+        <v>28.20673730238359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -701,12 +735,14 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -733,19 +769,25 @@
         <v>2.9513</v>
       </c>
       <c r="F9" t="n">
-        <v>10.6395810188858</v>
+        <v>9.700522613269881</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -772,19 +814,25 @@
         <v>18.5664</v>
       </c>
       <c r="F10" t="n">
-        <v>25.3151823301077</v>
+        <v>28.98629745006739</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -812,12 +860,14 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -845,12 +895,14 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -877,19 +929,25 @@
         <v>29.6559</v>
       </c>
       <c r="F13" t="n">
-        <v>21.3817669393666</v>
+        <v>26.73704928902369</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -915,16 +973,28 @@
       <c r="E14" t="n">
         <v>3.0925</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>instant</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>unmeasurable workbook bin</t>
+      <c r="F14" t="n">
+        <v>11.4348704758405</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
@@ -950,12 +1020,14 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -983,12 +1055,14 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1016,12 +1090,14 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1049,12 +1125,14 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1081,19 +1159,25 @@
         <v>7.953</v>
       </c>
       <c r="F19" t="n">
-        <v>21.0901140090582</v>
+        <v>21.84864567532638</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1119,16 +1203,28 @@
       <c r="E20" t="n">
         <v>4.8602</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>unmeasurable workbook bin</t>
+      <c r="F20" t="n">
+        <v>11.6923076923076</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1250,14 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1186,19 +1284,25 @@
         <v>19.0456</v>
       </c>
       <c r="F22" t="n">
-        <v>20.6207473711021</v>
+        <v>31.0665463857562</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1224,16 +1328,28 @@
       <c r="E23" t="n">
         <v>10.3172</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>unmeasurable workbook bin</t>
+      <c r="F23" t="n">
+        <v>14.2222222222222</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1375,14 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1290,16 +1408,28 @@
       <c r="E25" t="n">
         <v>9.0303</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>slow</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>unmeasurable workbook bin</t>
+      <c r="F25" t="n">
+        <v>17.7777777777777</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>measurable</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>k_corrected &gt; 0</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1455,14 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1358,12 +1490,14 @@
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1391,12 +1525,14 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1424,12 +1560,14 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1457,12 +1595,14 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1490,12 +1630,14 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1523,12 +1665,14 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1562,12 +1706,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1601,12 +1751,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1634,12 +1790,14 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1666,19 +1824,25 @@
         <v>24.5018</v>
       </c>
       <c r="F36" t="n">
-        <v>71.111111111111</v>
+        <v>71.11111111111099</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1706,12 +1870,14 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1739,12 +1905,14 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1771,19 +1939,25 @@
         <v>10.3793</v>
       </c>
       <c r="F39" t="n">
-        <v>7.35213830755232</v>
+        <v>7.352138307552319</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1811,12 +1985,14 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1850,12 +2026,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1883,12 +2065,14 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -1922,12 +2106,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1954,19 +2144,25 @@
         <v>65.768</v>
       </c>
       <c r="F44" t="n">
-        <v>232.727272727272</v>
+        <v>232.7272727272721</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -1993,19 +2189,25 @@
         <v>433.5306</v>
       </c>
       <c r="F45" t="n">
-        <v>853.333333333333</v>
+        <v>853.3333333333331</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2039,12 +2241,18 @@
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2072,12 +2280,14 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -2111,12 +2321,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2150,12 +2366,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2183,12 +2405,14 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -2216,12 +2440,14 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -2255,12 +2481,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2294,12 +2526,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2325,22 +2563,18 @@
       <c r="E54" t="n">
         <v>3.6466</v>
       </c>
-      <c r="F54" t="n">
-        <v>7.35632183908046</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>measurable</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>k_corrected &gt; 0</t>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2598,18 @@
       <c r="E55" t="n">
         <v>101.8586</v>
       </c>
-      <c r="F55" t="n">
-        <v>222.608695652173</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>low_confidence_order_of_magnitude</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>measurable</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>k_corrected &gt; 0</t>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>unmeasurable workbook bin</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2641,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2444,12 +2680,14 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -2476,19 +2714,25 @@
         <v>12.9576</v>
       </c>
       <c r="F58" t="n">
-        <v>21.0526315789473</v>
+        <v>20.9749171793658</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>high_confidence</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+          <t>medium_confidence</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2522,12 +2766,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2554,19 +2804,25 @@
         <v>113.83</v>
       </c>
       <c r="F60" t="n">
-        <v>120</v>
+        <v>159.9999999999999</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>medium_confidence</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+          <t>low_confidence_order_of_magnitude</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2600,12 +2856,18 @@
           <t>high_confidence</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -2635,6 +2897,8 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2660,6 +2924,8 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2685,6 +2951,8 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2710,6 +2978,8 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2735,6 +3005,8 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2760,6 +3032,8 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2785,6 +3059,8 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2810,6 +3086,8 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2835,6 +3113,8 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2860,6 +3140,8 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2885,6 +3167,8 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2910,6 +3194,8 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2935,6 +3221,8 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2960,6 +3248,8 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2985,6 +3275,8 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3010,6 +3302,8 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3035,6 +3329,8 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3060,6 +3356,8 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3085,6 +3383,8 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3110,6 +3410,8 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3135,6 +3437,8 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3160,6 +3464,8 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3185,6 +3491,8 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3210,6 +3518,8 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3235,6 +3545,8 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3260,6 +3572,8 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3285,6 +3599,8 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3310,6 +3626,8 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3335,6 +3653,8 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3360,6 +3680,8 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3385,6 +3707,8 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3410,6 +3734,8 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3435,6 +3761,8 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3457,19 +3785,25 @@
         <v>18.9571</v>
       </c>
       <c r="F95" t="n">
-        <v>30.616958099637</v>
+        <v>30.61695809963701</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3497,12 +3831,14 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3536,12 +3872,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3569,12 +3911,14 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3601,19 +3945,25 @@
         <v>48.7922</v>
       </c>
       <c r="F99" t="n">
-        <v>91.0091743119265</v>
+        <v>91.00917431192653</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3641,12 +3991,14 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3680,12 +4032,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3719,12 +4077,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3752,12 +4116,14 @@
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3785,12 +4151,14 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3824,12 +4192,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3863,12 +4237,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -3896,12 +4276,14 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3929,12 +4311,14 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
         <is>
           <t>instant</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -3961,19 +4345,25 @@
         <v>6.5766</v>
       </c>
       <c r="F109" t="n">
-        <v>37.0235237638022</v>
+        <v>37.02352376380221</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4001,12 +4391,14 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4034,12 +4426,14 @@
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
         <is>
           <t>instant</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4067,12 +4461,14 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4106,12 +4502,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4139,12 +4541,14 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
         <is>
           <t>instant</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4178,12 +4582,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4217,12 +4627,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4250,12 +4666,14 @@
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4289,12 +4707,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4328,12 +4752,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4360,19 +4790,25 @@
         <v>24.9989</v>
       </c>
       <c r="F120" t="n">
-        <v>75.2941176470588</v>
+        <v>75.29411764705881</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4400,12 +4836,14 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4433,12 +4871,14 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4472,12 +4912,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4505,12 +4951,14 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4538,12 +4986,14 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr">
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>unmeasurable workbook bin</t>
         </is>
@@ -4577,12 +5027,18 @@
           <t>medium_confidence</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4616,12 +5072,18 @@
           <t>low_confidence_order_of_magnitude</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>measurable</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>k_corrected &gt; 0</t>
         </is>
@@ -4651,6 +5113,8 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4676,6 +5140,8 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4701,6 +5167,8 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4726,6 +5194,8 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4751,6 +5221,8 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4776,6 +5248,8 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4801,6 +5275,8 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4826,6 +5302,8 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4851,6 +5329,8 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4876,6 +5356,8 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4901,6 +5383,8 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4926,6 +5410,8 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4951,6 +5437,8 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4976,6 +5464,8 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5001,6 +5491,8 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5026,6 +5518,8 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5051,6 +5545,8 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5076,6 +5572,8 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5101,6 +5599,8 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5126,6 +5626,8 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5151,6 +5653,8 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5176,6 +5680,8 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5201,6 +5707,8 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5226,6 +5734,8 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5251,6 +5761,8 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5276,6 +5788,8 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
